--- a/evaluation_surveys/011_corporate_sustainability_maturity_survey--evaluation_surveys.xlsx
+++ b/evaluation_surveys/011_corporate_sustainability_maturity_survey--evaluation_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Corporate Sustainability Maturity Survey</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Corporate Sustainability Performance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maturity Levels</t>
+          <t>Sustainability Domains</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Sustainability Challenges</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Sustainability Strategy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>This is a free text question</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -643,17 +647,21 @@
           <t>Maturity Levels</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter a number between 1 and 10</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +671,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Future Sustainability Domains</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +694,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Corporate Sustainability Maturity Survey</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Page 8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide a detailed description</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,20 +721,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sustainability Domains</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Potential Benefits of Sustainability</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide a detailed description</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,13 +748,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sustainability Domains</t>
+          <t>Benchmarking</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -757,8 +773,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +802,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -803,12 +819,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -820,12 +836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -837,12 +853,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -854,12 +870,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -871,12 +887,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -888,12 +904,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -905,12 +921,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -922,63 +938,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -990,12 +1006,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1023,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1040,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
